--- a/product_selector_out/STM32G4 series.xlsx
+++ b/product_selector_out/STM32G4 series.xlsx
@@ -17670,7 +17670,7 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -45169,9 +45169,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -45234,14 +45234,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
@@ -45389,14 +45389,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW62" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY62" s="8" t="inlineStr">
@@ -45469,9 +45469,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47131,9 +47131,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -47196,14 +47196,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -47351,14 +47351,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY68" s="8" t="inlineStr">
@@ -47431,9 +47431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47458,9 +47458,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -47523,14 +47523,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T69" s="6" t="inlineStr">
@@ -47678,14 +47678,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW69" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY69" s="8" t="inlineStr">
@@ -47758,9 +47758,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52690,9 +52690,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -52755,14 +52755,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R85" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S85" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T85" s="6" t="inlineStr">
@@ -52910,14 +52910,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY85" s="8" t="inlineStr">
@@ -52990,9 +52990,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55954,7 +55954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D293"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -56047,7 +56047,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56113,7 +56113,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56179,7 +56179,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56245,7 +56245,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56311,7 +56311,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56377,7 +56377,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56443,7 +56443,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56509,7 +56509,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56575,7 +56575,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56641,7 +56641,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56707,7 +56707,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56773,7 +56773,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56839,7 +56839,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56905,7 +56905,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -56971,7 +56971,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57037,7 +57037,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57103,7 +57103,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57169,7 +57169,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57235,7 +57235,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57301,7 +57301,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57367,7 +57367,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57433,7 +57433,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57499,7 +57499,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57565,7 +57565,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57631,7 +57631,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57719,7 +57719,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57807,7 +57807,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57895,7 +57895,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -57983,7 +57983,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58071,7 +58071,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58137,7 +58137,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58225,7 +58225,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58291,7 +58291,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58379,7 +58379,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58467,7 +58467,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58533,7 +58533,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58621,7 +58621,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58709,7 +58709,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58797,7 +58797,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58863,7 +58863,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -58951,7 +58951,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59017,7 +59017,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59105,7 +59105,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59193,7 +59193,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59281,7 +59281,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59369,7 +59369,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59457,7 +59457,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59545,7 +59545,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59611,7 +59611,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59677,7 +59677,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59706,12 +59706,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -59721,19 +59721,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -59743,14 +59743,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32G4A1KE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -59765,7 +59765,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59777,7 +59777,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -59787,19 +59787,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -59809,19 +59809,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -59831,19 +59831,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -59853,19 +59853,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -59875,19 +59875,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -59897,14 +59897,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -59919,7 +59919,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -59931,7 +59931,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -59941,19 +59941,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -59963,19 +59963,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -59985,19 +59985,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -60007,7 +60007,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60019,7 +60019,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -60029,19 +60029,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -60051,19 +60051,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -60073,19 +60073,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -60095,7 +60095,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -60107,7 +60107,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -60117,19 +60117,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -60139,19 +60139,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -60161,19 +60161,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -60183,19 +60183,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -60205,19 +60205,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -60227,19 +60227,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32G4A1ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -60249,19 +60249,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -60271,19 +60271,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -60293,19 +60293,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32G4A1RE</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -60315,19 +60315,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -60337,19 +60337,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -60359,19 +60359,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -60381,19 +60381,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -60403,19 +60403,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -60425,19 +60425,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -60447,19 +60447,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -60469,19 +60469,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -60491,19 +60491,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -60513,19 +60513,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -60535,19 +60535,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -60557,19 +60557,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -60579,19 +60579,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -60601,19 +60601,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -60623,19 +60623,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -60645,19 +60645,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -60667,19 +60667,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -60689,19 +60689,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -60711,19 +60711,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -60733,19 +60733,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -60755,19 +60755,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -60777,19 +60777,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -60799,19 +60799,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -60821,19 +60821,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -60843,19 +60843,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -60865,19 +60865,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -60887,19 +60887,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -60909,19 +60909,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -60931,19 +60931,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -60953,19 +60953,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -60975,19 +60975,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -60997,19 +60997,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -61019,19 +61019,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -61041,19 +61041,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -61063,19 +61063,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -61085,19 +61085,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -61107,19 +61107,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -61129,19 +61129,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -61151,19 +61151,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -61173,19 +61173,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -61195,19 +61195,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -61217,19 +61217,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -61239,19 +61239,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -61261,19 +61261,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -61283,19 +61283,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -61305,19 +61305,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -61327,19 +61327,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -61349,19 +61349,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -61371,19 +61371,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -61393,19 +61393,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -61415,19 +61415,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -61437,19 +61437,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -61459,19 +61459,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -61481,19 +61481,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -61503,19 +61503,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -61525,19 +61525,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -61547,19 +61547,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -61569,19 +61569,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -61591,19 +61591,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STM32G4A1VE</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -61613,14 +61613,14 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -61635,14 +61635,14 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -61664,7 +61664,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -61679,14 +61679,14 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -61708,7 +61708,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -61723,14 +61723,14 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -61752,7 +61752,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -61767,14 +61767,14 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -61796,7 +61796,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -61811,14 +61811,14 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -61840,7 +61840,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -61855,14 +61855,14 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -61884,7 +61884,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -61899,14 +61899,14 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -61928,7 +61928,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -61943,14 +61943,14 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431K8</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -61972,7 +61972,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -61987,14 +61987,14 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -62009,14 +62009,14 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -62031,14 +62031,14 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G491CE</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -62060,7 +62060,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -62075,14 +62075,14 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -62097,14 +62097,14 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -62119,14 +62119,14 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G491CC</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -62140,270 +62140,6 @@
         </is>
       </c>
       <c r="D281" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>STM32G431K8</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>STM32G491CE</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>STM32G491CC</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32G4 series.xlsx
+++ b/product_selector_out/STM32G4 series.xlsx
@@ -17670,7 +17670,7 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
     </row>
@@ -45169,9 +45169,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -45234,14 +45234,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T62" s="6" t="inlineStr">
@@ -45389,14 +45389,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX62" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX62" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY62" s="8" t="inlineStr">
@@ -45469,9 +45469,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM62" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -47131,9 +47131,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -47196,14 +47196,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -47351,14 +47351,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY68" s="8" t="inlineStr">
@@ -47431,9 +47431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -47458,9 +47458,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -47523,14 +47523,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T69" s="6" t="inlineStr">
@@ -47678,14 +47678,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX69" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX69" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY69" s="8" t="inlineStr">
@@ -47758,9 +47758,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM69" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52690,9 +52690,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -52755,14 +52755,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T85" s="6" t="inlineStr">
@@ -52910,14 +52910,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY85" s="8" t="inlineStr">
@@ -52990,9 +52990,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55954,7 +55954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -59706,12 +59706,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -59721,19 +59721,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -59743,14 +59743,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STM32G431V8</t>
+          <t>STM32G4A1KE</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -59777,7 +59777,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -59787,19 +59787,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -59809,19 +59809,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -59831,19 +59831,19 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>STM32G4A1CE</t>
+          <t>STM32G431V8</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -59853,19 +59853,19 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -59875,19 +59875,19 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -59897,14 +59897,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>STM32G431CB</t>
+          <t>STM32G4A1CE</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -59931,7 +59931,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -59941,19 +59941,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -59963,19 +59963,19 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -59985,19 +59985,19 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>STM32G431V6</t>
+          <t>STM32G431CB</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -60007,7 +60007,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -60019,7 +60019,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -60029,19 +60029,19 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -60051,19 +60051,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -60073,19 +60073,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STM32G431RB</t>
+          <t>STM32G431V6</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -60095,7 +60095,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
@@ -60107,7 +60107,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -60117,19 +60117,19 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -60139,19 +60139,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -60161,19 +60161,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G431RB</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -60183,19 +60183,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STM32G431M6</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -60205,19 +60205,19 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -60227,19 +60227,19 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1ME</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -60249,19 +60249,19 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -60271,19 +60271,19 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>STM32G491VE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -60293,19 +60293,19 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G4A1RE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -60315,19 +60315,19 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -60337,19 +60337,19 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -60359,19 +60359,19 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>STM32G491RE</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -60381,19 +60381,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G431M6</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -60403,19 +60403,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -60425,19 +60425,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -60447,19 +60447,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>STM32G491RC</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -60469,19 +60469,19 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491VE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -60491,19 +60491,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -60513,19 +60513,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -60535,19 +60535,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>STM32G491ME</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -60557,19 +60557,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RE</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -60579,19 +60579,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -60601,19 +60601,19 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP64, UFBGA4, WLCSP64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>STM32G441VB</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -60623,19 +60623,19 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -60645,19 +60645,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491RC</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -60667,19 +60667,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -60689,19 +60689,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>STM32G491MC</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -60711,19 +60711,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -60733,19 +60733,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G491ME</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -60755,19 +60755,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>STM32G441RB</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -60777,19 +60777,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -60799,19 +60799,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G441VB</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -60821,19 +60821,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -60843,19 +60843,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>STM32G491KE</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -60865,19 +60865,19 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -60887,19 +60887,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G491MC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -60909,19 +60909,19 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -60931,19 +60931,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>STM32G491KC</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -60953,19 +60953,19 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G441RB</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -60975,19 +60975,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -60997,19 +60997,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>STM32G441CB</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -61019,19 +61019,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -61041,19 +61041,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KE</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -61063,19 +61063,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -61085,19 +61085,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>STM32G491VC</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -61107,19 +61107,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -61129,19 +61129,19 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G491KC</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -61151,19 +61151,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -61173,19 +61173,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STM32G431K6</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -61195,19 +61195,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G441CB</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -61217,19 +61217,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -61239,19 +61239,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP100 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>STM32G441MB</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -61261,19 +61261,19 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -61283,19 +61283,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G491VC</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -61305,19 +61305,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -61327,19 +61327,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>STM32G431R8</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -61349,19 +61349,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -61371,19 +61371,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G431K6</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -61393,19 +61393,19 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -61415,19 +61415,19 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>STM32G431R6</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -61437,19 +61437,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G441MB</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -61459,19 +61459,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -61481,19 +61481,19 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -61503,19 +61503,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>STM32G431M8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -61525,19 +61525,19 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G431R8</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Operating Temperature (°C) max</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -61547,19 +61547,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -61569,19 +61569,19 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -61591,19 +61591,19 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 7. Timer feature comparison (continued) lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>STM32G431C8</t>
+          <t>STM32G4A1VE</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Operating Temperature (°C) max</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -61613,14 +61613,14 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -61635,14 +61635,14 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP64, UFBGA64 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -61664,7 +61664,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -61686,7 +61686,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>STM32G431MB</t>
+          <t>STM32G431R6</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -61708,7 +61708,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -61723,14 +61723,14 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -61752,7 +61752,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -61774,7 +61774,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>STM32G431C6</t>
+          <t>STM32G431M8</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -61796,7 +61796,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -61811,14 +61811,14 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -61840,7 +61840,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -61862,7 +61862,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>STM32G431KB</t>
+          <t>STM32G431C8</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -61884,7 +61884,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -61899,14 +61899,14 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP80 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -61928,7 +61928,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -61950,7 +61950,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>STM32G431K8</t>
+          <t>STM32G431MB</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -61972,7 +61972,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -61987,14 +61987,14 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP48, UFQFPN48, WLCSP49 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -62009,14 +62009,14 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -62038,7 +62038,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>STM32G491CE</t>
+          <t>STM32G431C6</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -62060,7 +62060,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -62075,14 +62075,14 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -62097,14 +62097,14 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>STM32G491CC</t>
+          <t>STM32G431KB</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -62126,20 +62126,284 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
+          <t>STM32G431KB</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts lists LQFP32, UFQFPN32 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G431x6/x8/xB features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>STM32G431K8</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>STM32G491CE</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Operating Temperature (°C) max</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
           <t>STM32G491CC</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Other timer functions</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Table 2. STM32G491xC/xE features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Table 17. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>STM32G491CC</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
         <is>
           <t>Operating Temperature (°C) max</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C293" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D293" t="inlineStr">
         <is>
           <t>Ambient operating temperature: -40 to 85 °C / -40 to 125 °C (datasheet offers 2 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32G4 series.xlsx
+++ b/product_selector_out/STM32G4 series.xlsx
@@ -17108,7 +17108,7 @@
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S61" s="4" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S63" s="4" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S65" s="4" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="R66" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S66" s="4" t="inlineStr">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S67" s="4" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="R70" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S70" s="4" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S71" s="4" t="inlineStr">
@@ -20705,7 +20705,7 @@
       </c>
       <c r="R72" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S72" s="4" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S73" s="4" t="inlineStr">
@@ -21359,7 +21359,7 @@
       </c>
       <c r="R74" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S74" s="4" t="inlineStr">
@@ -22013,7 +22013,7 @@
       </c>
       <c r="R76" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S76" s="4" t="inlineStr">
@@ -22667,7 +22667,7 @@
       </c>
       <c r="R78" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S78" s="4" t="inlineStr">
@@ -22994,7 +22994,7 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S79" s="4" t="inlineStr">
@@ -23648,7 +23648,7 @@
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S81" s="4" t="inlineStr">
@@ -23975,7 +23975,7 @@
       </c>
       <c r="R82" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S82" s="4" t="inlineStr">
@@ -24629,7 +24629,7 @@
       </c>
       <c r="R84" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S84" s="4" t="inlineStr">
@@ -25283,7 +25283,7 @@
       </c>
       <c r="R86" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S86" s="4" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S87" s="4" t="inlineStr">
@@ -25937,7 +25937,7 @@
       </c>
       <c r="R88" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S88" s="4" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S89" s="4" t="inlineStr">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="R90" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S90" s="4" t="inlineStr">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S91" s="4" t="inlineStr">
@@ -27245,7 +27245,7 @@
       </c>
       <c r="R92" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S92" s="4" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="R93" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S93" s="4" t="inlineStr">
@@ -27899,7 +27899,7 @@
       </c>
       <c r="R94" s="4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S94" s="4" t="inlineStr">

--- a/product_selector_out/STM32G4 series.xlsx
+++ b/product_selector_out/STM32G4 series.xlsx
@@ -9038,7 +9038,7 @@
       </c>
       <c r="AM36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN36" s="4" t="inlineStr">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="AM53" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN53" s="4" t="inlineStr">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="AM55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN55" s="4" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="AM78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN78" s="4" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="AM79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN79" s="4" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="AM82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN82" s="4" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="AM91" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN91" s="4" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="AM92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AN92" s="4" t="inlineStr">
@@ -36837,9 +36837,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN36" s="6" t="inlineStr">
@@ -37164,9 +37164,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN37" s="6" t="inlineStr">
@@ -37491,9 +37491,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN38" s="6" t="inlineStr">
@@ -37818,9 +37818,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN39" s="6" t="inlineStr">
@@ -38145,9 +38145,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN40" s="6" t="inlineStr">
@@ -38799,9 +38799,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN42" s="6" t="inlineStr">
@@ -39453,9 +39453,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN44" s="6" t="inlineStr">
@@ -39780,9 +39780,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN45" s="6" t="inlineStr">
@@ -40434,9 +40434,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN47" s="6" t="inlineStr">
@@ -40761,9 +40761,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM48" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN48" s="6" t="inlineStr">
@@ -41088,9 +41088,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM49" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN49" s="6" t="inlineStr">
@@ -41742,9 +41742,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM51" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM51" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN51" s="6" t="inlineStr">
@@ -42396,9 +42396,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM53" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM53" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN53" s="6" t="inlineStr">
@@ -42723,9 +42723,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN54" s="6" t="inlineStr">
@@ -43050,9 +43050,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM55" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM55" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN55" s="6" t="inlineStr">
@@ -43377,9 +43377,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN56" s="6" t="inlineStr">
@@ -43704,9 +43704,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM57" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM57" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN57" s="6" t="inlineStr">
@@ -44031,9 +44031,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM58" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM58" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN58" s="6" t="inlineStr">
@@ -45012,9 +45012,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN61" s="6" t="inlineStr">
@@ -45666,9 +45666,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM63" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM63" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN63" s="6" t="inlineStr">
@@ -46647,9 +46647,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM66" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM66" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN66" s="6" t="inlineStr">
@@ -46974,9 +46974,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN67" s="6" t="inlineStr">
@@ -47955,9 +47955,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM70" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN70" s="6" t="inlineStr">
@@ -48282,9 +48282,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN71" s="6" t="inlineStr">
@@ -48609,9 +48609,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN72" s="6" t="inlineStr">
@@ -48936,9 +48936,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM73" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN73" s="6" t="inlineStr">
@@ -49263,9 +49263,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN74" s="6" t="inlineStr">
@@ -49917,9 +49917,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN76" s="6" t="inlineStr">
@@ -50571,9 +50571,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM78" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM78" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN78" s="6" t="inlineStr">
@@ -50898,9 +50898,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM79" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN79" s="6" t="inlineStr">
@@ -51552,9 +51552,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN81" s="6" t="inlineStr">
@@ -51879,9 +51879,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM82" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN82" s="6" t="inlineStr">
@@ -52533,9 +52533,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN84" s="6" t="inlineStr">
@@ -53187,9 +53187,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN86" s="6" t="inlineStr">
@@ -53514,9 +53514,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN87" s="6" t="inlineStr">
@@ -54168,9 +54168,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM89" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM89" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN89" s="6" t="inlineStr">
@@ -54822,9 +54822,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM91" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM91" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN91" s="6" t="inlineStr">
@@ -55149,9 +55149,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM92" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AM92" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN92" s="6" t="inlineStr">

--- a/product_selector_out/STM32G4 series.xlsx
+++ b/product_selector_out/STM32G4 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM94"/>
+  <dimension ref="A1:BN94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.984375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g483ce.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g473cb.pdf</t>
         </is>
       </c>
@@ -9168,6 +9295,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -11130,6 +11287,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -11457,6 +11619,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -11784,6 +11951,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -12111,6 +12283,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -12438,6 +12615,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -12765,6 +12947,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -13092,6 +13279,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -13419,6 +13611,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -13746,6 +13943,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -14073,6 +14275,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -14400,6 +14607,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -14727,6 +14939,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -15054,6 +15271,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -15381,6 +15603,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -15708,6 +15935,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -16035,6 +16267,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -16362,6 +16599,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g474cb.pdf</t>
         </is>
       </c>
@@ -16689,6 +16931,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g484ce.pdf</t>
         </is>
       </c>
@@ -17016,6 +17263,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -17343,6 +17595,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -17670,6 +17927,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -17997,6 +18259,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -18324,6 +18591,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -18651,6 +18923,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -18978,6 +19255,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -19305,6 +19587,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -19632,6 +19919,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -19959,6 +20251,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -20286,6 +20583,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -20613,6 +20915,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -20940,6 +21247,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -21267,6 +21579,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -21594,6 +21911,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -21921,6 +22243,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -22248,6 +22575,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -22575,6 +22907,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -22902,6 +23239,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -23229,6 +23571,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -23556,6 +23903,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -23883,6 +24235,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -24210,6 +24567,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -24537,6 +24899,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g441cb.pdf</t>
         </is>
       </c>
@@ -24864,6 +25231,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -25191,6 +25563,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g4a1ce.pdf</t>
         </is>
       </c>
@@ -25518,6 +25895,11 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -25845,6 +26227,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -26172,6 +26559,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -26499,6 +26891,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -26826,6 +27223,11 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -27153,6 +27555,11 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -27480,6 +27887,11 @@
       </c>
       <c r="BM92" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g431c6.pdf</t>
         </is>
       </c>
@@ -27807,6 +28219,11 @@
       </c>
       <c r="BM93" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
@@ -28134,12 +28551,17 @@
       </c>
       <c r="BM94" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g491cc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -28160,16 +28582,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -28182,6 +28602,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -28201,7 +28622,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -28301,7 +28724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM94"/>
+  <dimension ref="A1:BN94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28369,6 +28792,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28702,6 +29126,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -28797,6 +29226,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -29119,7 +29549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29446,7 +29881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29773,7 +30213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30100,7 +30545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30427,7 +30877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30754,7 +31209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31081,7 +31541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31408,7 +31873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31735,7 +32205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32062,7 +32537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32389,7 +32869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32716,7 +33201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33043,7 +33533,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33370,7 +33865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33697,7 +34197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34024,7 +34529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34351,7 +34861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34678,7 +35193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35005,7 +35525,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35332,7 +35857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35659,7 +36189,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35986,7 +36521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36313,7 +36853,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36640,7 +37185,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36967,7 +37517,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37294,7 +37849,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37621,7 +38181,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37948,7 +38513,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38275,7 +38845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38602,7 +39177,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38929,7 +39509,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39256,7 +39841,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39583,7 +40173,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39910,7 +40505,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40237,7 +40837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40564,7 +41169,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40891,7 +41501,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41218,7 +41833,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41545,7 +42165,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41872,7 +42497,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42199,7 +42829,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42526,7 +43161,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42853,7 +43493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43180,7 +43825,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43507,7 +44157,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43834,7 +44489,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44161,7 +44821,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44488,7 +45153,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44815,7 +45485,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45142,7 +45817,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45469,7 +46149,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45796,7 +46481,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46123,7 +46813,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46450,7 +47145,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46777,7 +47477,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47104,7 +47809,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47431,7 +48141,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47758,7 +48473,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48085,7 +48805,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48412,7 +49137,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48739,7 +49469,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49066,7 +49801,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49393,7 +50133,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49720,7 +50465,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50047,7 +50797,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50374,7 +51129,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50701,7 +51461,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51028,7 +51793,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51355,7 +52125,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51682,7 +52457,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52009,7 +52789,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52336,7 +53121,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52663,7 +53453,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52990,7 +53785,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53317,7 +54117,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
+      <c r="BM86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53644,7 +54449,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53971,7 +54781,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54298,7 +55113,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54625,7 +55445,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
+      <c r="BM90" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54952,7 +55777,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55279,7 +56109,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM92" s="6" t="inlineStr">
+      <c r="BM92" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55606,7 +56441,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM93" s="6" t="inlineStr">
+      <c r="BM93" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55933,7 +56773,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM94" s="6" t="inlineStr">
+      <c r="BM94" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55941,8 +56786,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
